--- a/src/BexioOrderImport.Format.EanList.Tests/Fixtures/EanListOrder.xlsx
+++ b/src/BexioOrderImport.Format.EanList.Tests/Fixtures/EanListOrder.xlsx
@@ -401,7 +401,7 @@
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="0">
-        <x:v>7612345678904</x:v>
+        <x:v>7612345678900</x:v>
       </x:c>
       <x:c r="B2" s="0">
         <x:v>3</x:v>
@@ -449,7 +449,7 @@
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="0">
-        <x:v>7612345678904</x:v>
+        <x:v>826710896036</x:v>
       </x:c>
       <x:c r="B9" s="0">
         <x:v>5</x:v>
